--- a/crl_results.xlsx
+++ b/crl_results.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -866,6 +866,447 @@
       <c r="M8" s="1" t="inlineStr">
         <is>
           <t>21.10 ± 29.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>--- NEW RUN: C-LAMAML (dt=0.5, dc=0.3) vs CRL vs Random ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="J11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="L11" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="M11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>300</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>88.48 ± 104.72</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.03 ± 0.30</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>82.20 ± 105.01</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>185.46 ± 108.69</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>18.48 ± 25.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>300</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>87.68 ± 113.53</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>73.06 ± 98.78</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>174.07 ± 116.53</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>18.48 ± 29.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>300</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>79.82 ± 105.73</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>79.08 ± 104.35</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>203.58 ± 107.99</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>19.48 ± 24.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" t="n">
+        <v>300</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>90.25 ± 103.66</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.10</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>90.31 ± 109.77</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>209.26 ± 109.04</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>21.21 ± 31.49</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>300</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>112.60 ± 104.57</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>77.45 ± 92.54</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>208.80 ± 103.92</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>16.99 ± 24.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>300</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>106.10 ± 112.62</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.03 ± 0.30</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>100.23 ± 110.71</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>232.08 ± 94.06</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>22.63 ± 29.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr"/>
+      <c r="C18" s="1" t="inlineStr"/>
+      <c r="D18" s="1" t="inlineStr"/>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>94.16 ± 108.15</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.18</t>
+        </is>
+      </c>
+      <c r="H18" s="1" t="inlineStr">
+        <is>
+          <t>83.72 ± 104.11</t>
+        </is>
+      </c>
+      <c r="I18" s="1" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="J18" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K18" s="1" t="inlineStr">
+        <is>
+          <t>202.21 ± 108.51</t>
+        </is>
+      </c>
+      <c r="L18" s="1" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M18" s="1" t="inlineStr">
+        <is>
+          <t>19.55 ± 27.48</t>
         </is>
       </c>
     </row>
@@ -880,7 +1321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1314,6 +1755,447 @@
       <c r="M8" s="1" t="inlineStr">
         <is>
           <t>38.94 ± 39.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>--- NEW RUN: C-LAMAML (dt=0.5, dc=0.3) vs CRL vs Random ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="J11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="L11" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="M11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>300</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>131.64 ± 132.83</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.04 ± 0.31</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>149.48 ± 126.61</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>215.31 ± 105.40</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>50.61 ± 45.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>300</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>128.09 ± 133.96</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2.15 ± 21.29</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>132.17 ± 134.44</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>194.07 ± 116.54</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>38.67 ± 44.37</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>300</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>133.59 ± 125.28</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.04 ± 0.24</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>129.55 ± 124.65</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>198.29 ± 111.37</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>37.18 ± 40.77</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" t="n">
+        <v>300</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>126.88 ± 126.58</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.14</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>121.12 ± 124.52</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.20</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>208.68 ± 111.17</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>35.69 ± 36.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>300</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>124.97 ± 116.79</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.10</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>126.16 ± 121.73</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>232.06 ± 103.60</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>40.18 ± 34.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>300</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>129.88 ± 118.33</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.04 ± 0.24</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>118.70 ± 117.97</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>248.32 ± 83.29</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>42.95 ± 35.94</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr"/>
+      <c r="C18" s="1" t="inlineStr"/>
+      <c r="D18" s="1" t="inlineStr"/>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>129.18 ± 125.83</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>0.38 ± 8.73</t>
+        </is>
+      </c>
+      <c r="H18" s="1" t="inlineStr">
+        <is>
+          <t>129.53 ± 125.49</t>
+        </is>
+      </c>
+      <c r="I18" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J18" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.08</t>
+        </is>
+      </c>
+      <c r="K18" s="1" t="inlineStr">
+        <is>
+          <t>216.12 ± 107.45</t>
+        </is>
+      </c>
+      <c r="L18" s="1" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M18" s="1" t="inlineStr">
+        <is>
+          <t>40.88 ± 40.25</t>
         </is>
       </c>
     </row>
@@ -1328,7 +2210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1501,6 +2383,186 @@
       <c r="M3" s="1" t="inlineStr">
         <is>
           <t>61.39 ± 62.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>--- NEW RUN: C-LAMAML (dt=0.5, dc=0.3) vs CRL vs Random ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="M6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>495.89 ± 423.48</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>7.34 ± 10.14</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>564.68 ± 437.82</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>747.11 ± 364.54</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>48.84 ± 48.76</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr"/>
+      <c r="D8" s="1" t="inlineStr"/>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>495.89 ± 423.48</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>7.34 ± 10.14</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>564.68 ± 437.82</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>747.11 ± 364.54</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M8" s="1" t="inlineStr">
+        <is>
+          <t>48.84 ± 48.76</t>
         </is>
       </c>
     </row>
@@ -1515,7 +2577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1906,6 +2968,404 @@
       <c r="M7" s="1" t="inlineStr">
         <is>
           <t>50.51 ± 51.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>--- NEW RUN: C-LAMAML (dt=0.5, dc=0.3) vs CRL vs Random ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="K10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="L10" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="M10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>800</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>663.95 ± 290.21</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>4.28 ± 6.78</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>649.55 ± 301.60</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>10.07 ± 21.52</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>583.62 ± 269.07</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>66.72 ± 56.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>800</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>524.13 ± 364.70</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>10.25 ± 16.72</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>481.87 ± 368.63</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>17.30 ± 34.32</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>610.25 ± 282.99</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>67.68 ± 69.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>800</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>521.23 ± 360.81</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>17.47 ± 33.96</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>540.05 ± 346.36</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>14.32 ± 27.18</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>669.13 ± 243.53</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>45.47 ± 39.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>800</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>623.47 ± 321.12</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>22.52 ± 48.61</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>629.55 ± 309.89</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>15.45 ± 26.95</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>651.02 ± 251.98</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>41.58 ± 44.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>800</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>546.72 ± 355.15</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>9.88 ± 24.36</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>554.40 ± 348.94</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>7.08 ± 14.44</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>690.78 ± 218.45</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>32.65 ± 35.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr"/>
+      <c r="C16" s="1" t="inlineStr"/>
+      <c r="D16" s="1" t="inlineStr"/>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>575.90 ± 344.44</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>12.88 ± 30.46</t>
+        </is>
+      </c>
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t>571.08 ± 341.58</t>
+        </is>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="J16" s="1" t="inlineStr">
+        <is>
+          <t>12.84 ± 26.02</t>
+        </is>
+      </c>
+      <c r="K16" s="1" t="inlineStr">
+        <is>
+          <t>640.96 ± 257.14</t>
+        </is>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M16" s="1" t="inlineStr">
+        <is>
+          <t>50.82 ± 52.60</t>
         </is>
       </c>
     </row>
@@ -1920,7 +3380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2354,6 +3814,447 @@
       <c r="M8" s="1" t="inlineStr">
         <is>
           <t>47.50 ± 44.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>--- NEW RUN: C-LAMAML (dt=0.5, dc=0.3) vs CRL vs Random ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="J11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="L11" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="M11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>500</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>295.07 ± 192.86</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2.33 ± 4.01</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>315.55 ± 208.72</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>5.34 ± 13.82</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>402.74 ± 161.51</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>66.35 ± 53.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>500</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>327.40 ± 203.74</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>4.37 ± 11.41</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>360.88 ± 201.81</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>12.61 ± 42.63</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>408.81 ± 158.99</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>60.62 ± 56.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>500</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>269.94 ± 208.42</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2.94 ± 5.95</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>293.97 ± 208.27</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>5.26 ± 7.09</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>395.98 ± 166.31</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>41.61 ± 36.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" t="n">
+        <v>500</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>316.44 ± 199.30</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>3.69 ± 6.55</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>346.63 ± 209.98</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>7.17 ± 15.95</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>385.18 ± 186.02</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>48.92 ± 37.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>500</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>282.17 ± 203.87</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1.81 ± 3.68</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>344.64 ± 204.50</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>5.03 ± 8.91</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>430.29 ± 146.71</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>37.10 ± 39.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>500</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>331.78 ± 206.52</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1.37 ± 2.29</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>393.19 ± 188.51</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>3.65 ± 6.56</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>440.40 ± 138.15</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>39.55 ± 38.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr"/>
+      <c r="C18" s="1" t="inlineStr"/>
+      <c r="D18" s="1" t="inlineStr"/>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>303.80 ± 203.83</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>2.75 ± 6.45</t>
+        </is>
+      </c>
+      <c r="H18" s="1" t="inlineStr">
+        <is>
+          <t>342.48 ± 206.20</t>
+        </is>
+      </c>
+      <c r="I18" s="1" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="J18" s="1" t="inlineStr">
+        <is>
+          <t>6.51 ± 20.36</t>
+        </is>
+      </c>
+      <c r="K18" s="1" t="inlineStr">
+        <is>
+          <t>410.57 ± 161.47</t>
+        </is>
+      </c>
+      <c r="L18" s="1" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="M18" s="1" t="inlineStr">
+        <is>
+          <t>49.02 ± 45.81</t>
         </is>
       </c>
     </row>
@@ -2368,7 +4269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2759,6 +4660,404 @@
       <c r="M7" s="1" t="inlineStr">
         <is>
           <t>73.99 ± 73.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>--- NEW RUN: C-LAMAML (dt=0.5, dc=0.3) vs CRL vs Random ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="K10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="L10" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="M10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>350.95 ± 470.05</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.09 ± 0.51</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>339.56 ± 460.61</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>581.58 ± 463.12</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>86.84 ± 90.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>366.53 ± 422.36</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.04 ± 0.24</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>360.48 ± 423.17</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>663.07 ± 436.07</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>78.16 ± 84.66</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>287.87 ± 373.97</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.11 ± 1.09</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>296.32 ± 383.32</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>742.14 ± 439.78</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>61.53 ± 56.97</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>343.15 ± 346.82</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.10</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>343.58 ± 363.33</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>892.24 ± 383.25</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>68.50 ± 56.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>367.11 ± 348.95</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.10</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>357.55 ± 367.81</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>908.51 ± 392.94</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>50.69 ± 38.87</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr"/>
+      <c r="C16" s="1" t="inlineStr"/>
+      <c r="D16" s="1" t="inlineStr"/>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>343.12 ± 396.35</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>0.05 ± 0.56</t>
+        </is>
+      </c>
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t>339.50 ± 402.02</t>
+        </is>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="J16" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K16" s="1" t="inlineStr">
+        <is>
+          <t>757.51 ± 442.81</t>
+        </is>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="M16" s="1" t="inlineStr">
+        <is>
+          <t>69.14 ± 69.41</t>
         </is>
       </c>
     </row>
@@ -2773,7 +5072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3164,6 +5463,404 @@
       <c r="M7" s="1" t="inlineStr">
         <is>
           <t>51.85 ± 50.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>--- NEW RUN: C-LAMAML (dt=0.5, dc=0.3) vs CRL vs Random ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="K10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="L10" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="M10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>800</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>528.89 ± 366.97</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>8.70 ± 26.14</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>270.90 ± 334.69</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>7.21 ± 18.31</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>502.43 ± 312.92</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>55.33 ± 62.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>800</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>512.42 ± 362.90</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>15.10 ± 39.26</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>266.93 ± 316.27</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>3.05 ± 6.78</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>522.52 ± 303.63</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>51.29 ± 47.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>800</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>460.87 ± 377.89</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>11.94 ± 34.54</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>286.60 ± 305.22</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>3.56 ± 7.68</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>567.50 ± 284.76</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>48.72 ± 42.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>800</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>452.46 ± 372.47</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>11.40 ± 49.28</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>283.31 ± 313.58</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2.99 ± 8.42</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>576.04 ± 274.62</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>40.84 ± 41.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>800</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>460.61 ± 374.08</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>11.27 ± 46.07</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>308.81 ± 314.51</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2.69 ± 11.50</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>637.48 ± 254.31</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>34.36 ± 33.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr"/>
+      <c r="C16" s="1" t="inlineStr"/>
+      <c r="D16" s="1" t="inlineStr"/>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>483.05 ± 372.22</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>11.68 ± 39.97</t>
+        </is>
+      </c>
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t>283.31 ± 317.34</t>
+        </is>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J16" s="1" t="inlineStr">
+        <is>
+          <t>3.90 ± 11.47</t>
+        </is>
+      </c>
+      <c r="K16" s="1" t="inlineStr">
+        <is>
+          <t>561.19 ± 290.62</t>
+        </is>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="M16" s="1" t="inlineStr">
+        <is>
+          <t>46.11 ± 47.25</t>
         </is>
       </c>
     </row>
@@ -3178,7 +5875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3506,6 +6203,341 @@
       <c r="M6" s="1" t="inlineStr">
         <is>
           <t>35.85 ± 73.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>--- NEW RUN: C-LAMAML (dt=0.5, dc=0.3) vs CRL vs Random ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="J9" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="K9" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="L9" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="M9" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>392.40 ± 418.61</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>16.99 ± 57.28</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>473.15 ± 425.88</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>19.82 ± 58.64</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>682.79 ± 390.48</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>58.67 ± 104.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>446.79 ± 424.19</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>21.56 ± 86.38</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>402.09 ± 420.66</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>6.12 ± 17.22</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>614.84 ± 408.98</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>24.70 ± 54.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>496.20 ± 426.63</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>21.62 ± 63.08</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>620.40 ± 423.78</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>19.35 ± 48.74</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>780.36 ± 358.42</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>44.27 ± 75.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>484.11 ± 415.66</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>18.74 ± 60.26</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>658.56 ± 428.83</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>19.64 ± 55.06</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>773.03 ± 372.63</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>38.25 ± 72.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr"/>
+      <c r="C14" s="1" t="inlineStr"/>
+      <c r="D14" s="1" t="inlineStr"/>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>454.88 ± 423.23</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>19.73 ± 67.77</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="inlineStr">
+        <is>
+          <t>538.55 ± 437.55</t>
+        </is>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="J14" s="1" t="inlineStr">
+        <is>
+          <t>16.23 ± 48.16</t>
+        </is>
+      </c>
+      <c r="K14" s="1" t="inlineStr">
+        <is>
+          <t>712.75 ± 389.15</t>
+        </is>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M14" s="1" t="inlineStr">
+        <is>
+          <t>41.47 ± 79.83</t>
         </is>
       </c>
     </row>
@@ -3520,7 +6552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3911,6 +6943,404 @@
       <c r="M7" s="1" t="inlineStr">
         <is>
           <t>11.67 ± 18.29</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>--- NEW RUN: C-LAMAML (dt=0.5, dc=0.3) vs CRL vs Random ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="K10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="L10" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="M10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>300</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>84.77 ± 85.89</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>72.80 ± 77.35</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>208.50 ± 111.67</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>9.59 ± 17.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>300</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>84.41 ± 93.87</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>75.28 ± 86.22</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>207.88 ± 109.14</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>9.83 ± 14.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="n">
+        <v>300</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>66.02 ± 81.11</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>87.50 ± 88.81</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>205.61 ± 112.17</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>11.91 ± 18.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" t="n">
+        <v>300</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>74.08 ± 71.08</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>93.22 ± 97.67</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>231.55 ± 97.00</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>12.80 ± 19.31</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" t="n">
+        <v>300</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>98.60 ± 99.07</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>100.00 ± 94.94</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>230.29 ± 104.95</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>13.48 ± 19.77</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr"/>
+      <c r="C16" s="1" t="inlineStr"/>
+      <c r="D16" s="1" t="inlineStr"/>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>81.58 ± 87.45</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t>85.76 ± 89.88</t>
+        </is>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J16" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K16" s="1" t="inlineStr">
+        <is>
+          <t>216.77 ± 107.76</t>
+        </is>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M16" s="1" t="inlineStr">
+        <is>
+          <t>11.52 ± 18.02</t>
         </is>
       </c>
     </row>
@@ -3925,7 +7355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4098,6 +7528,186 @@
       <c r="M3" s="1" t="inlineStr">
         <is>
           <t>27.60 ± 33.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>--- NEW RUN: C-LAMAML (dt=0.5, dc=0.3) vs CRL vs Random ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="M6" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>563.13 ± 440.94</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1.07 ± 3.15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>552.54 ± 433.08</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>707.10 ± 382.29</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>25.60 ± 27.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr"/>
+      <c r="D8" s="1" t="inlineStr"/>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>563.13 ± 440.94</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>1.07 ± 3.15</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t>552.54 ± 433.08</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J8" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>707.10 ± 382.29</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M8" s="1" t="inlineStr">
+        <is>
+          <t>25.60 ± 27.83</t>
         </is>
       </c>
     </row>
@@ -4112,7 +7722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4503,6 +8113,404 @@
       <c r="M7" s="1" t="inlineStr">
         <is>
           <t>24.47 ± 30.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>--- NEW RUN: C-LAMAML (dt=0.5, dc=0.3) vs CRL vs Random ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="K10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="L10" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="M10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>800</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>382.18 ± 353.45</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.22 ± 1.18</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>270.13 ± 332.20</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.13</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>475.92 ± 332.89</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>17.93 ± 26.09</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>800</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>211.83 ± 281.64</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.20 ± 1.18</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>315.47 ± 336.03</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.07 ± 0.51</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>638.18 ± 266.66</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>31.27 ± 39.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>800</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>307.80 ± 327.91</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.05 ± 0.28</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>303.05 ± 310.07</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.03 ± 0.18</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>617.38 ± 273.46</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>27.67 ± 36.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>800</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>370.10 ± 334.02</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.52 ± 3.22</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>406.80 ± 313.50</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>636.93 ± 262.40</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>16.77 ± 23.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>800</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>326.60 ± 304.70</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.03 ± 0.26</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>359.83 ± 320.50</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>716.65 ± 202.42</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>18.05 ± 19.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr"/>
+      <c r="C16" s="1" t="inlineStr"/>
+      <c r="D16" s="1" t="inlineStr"/>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>319.70 ± 326.94</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>0.20 ± 1.64</t>
+        </is>
+      </c>
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t>331.06 ± 326.11</t>
+        </is>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="J16" s="1" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.25</t>
+        </is>
+      </c>
+      <c r="K16" s="1" t="inlineStr">
+        <is>
+          <t>617.01 ± 281.85</t>
+        </is>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M16" s="1" t="inlineStr">
+        <is>
+          <t>22.34 ± 30.41</t>
         </is>
       </c>
     </row>
@@ -4517,7 +8525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4951,6 +8959,447 @@
       <c r="M8" s="1" t="inlineStr">
         <is>
           <t>25.16 ± 31.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>--- NEW RUN: C-LAMAML (dt=0.5, dc=0.3) vs CRL vs Random ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="J11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="L11" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="M11" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>500</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>249.43 ± 201.88</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.14</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>323.25 ± 210.14</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>405.33 ± 166.79</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>32.29 ± 36.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>500</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>288.22 ± 205.02</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.20</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>382.51 ± 195.49</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>399.27 ± 165.95</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>29.79 ± 35.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>500</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>268.24 ± 198.44</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>322.05 ± 212.89</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>399.23 ± 171.54</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>21.62 ± 24.89</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" t="n">
+        <v>500</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>249.27 ± 205.22</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.04 ± 0.28</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>311.88 ± 211.42</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>421.16 ± 155.09</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>23.23 ± 26.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>500</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>275.20 ± 203.09</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>348.27 ± 194.43</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>415.05 ± 148.31</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>13.60 ± 19.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>500</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>315.76 ± 196.48</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>364.42 ± 191.70</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>429.64 ± 143.67</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>18.39 ± 24.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr"/>
+      <c r="C18" s="1" t="inlineStr"/>
+      <c r="D18" s="1" t="inlineStr"/>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>274.35 ± 203.03</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.15</t>
+        </is>
+      </c>
+      <c r="H18" s="1" t="inlineStr">
+        <is>
+          <t>342.06 ± 204.45</t>
+        </is>
+      </c>
+      <c r="I18" s="1" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J18" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K18" s="1" t="inlineStr">
+        <is>
+          <t>411.61 ± 159.30</t>
+        </is>
+      </c>
+      <c r="L18" s="1" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M18" s="1" t="inlineStr">
+        <is>
+          <t>23.15 ± 29.20</t>
         </is>
       </c>
     </row>
@@ -4965,7 +9414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5356,6 +9805,404 @@
       <c r="M7" s="1" t="inlineStr">
         <is>
           <t>35.66 ± 43.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>--- NEW RUN: C-LAMAML (dt=0.5, dc=0.3) vs CRL vs Random ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="K10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="L10" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="M10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>238.75 ± 366.82</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.20</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>223.08 ± 334.15</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>601.06 ± 453.46</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>51.83 ± 65.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>250.66 ± 332.10</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>206.23 ± 262.73</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>707.68 ± 462.99</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>44.63 ± 56.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>286.25 ± 349.47</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>278.64 ± 324.00</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>741.56 ± 438.34</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>33.61 ± 36.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>327.39 ± 349.29</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.10</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>314.43 ± 349.70</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>852.94 ± 435.36</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>37.92 ± 37.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>383.77 ± 392.99</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.20</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>349.71 ± 375.49</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>825.10 ± 444.01</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>21.31 ± 25.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr"/>
+      <c r="C16" s="1" t="inlineStr"/>
+      <c r="D16" s="1" t="inlineStr"/>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>297.36 ± 362.64</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.13</t>
+        </is>
+      </c>
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t>274.42 ± 335.71</t>
+        </is>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="J16" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K16" s="1" t="inlineStr">
+        <is>
+          <t>745.67 ± 455.85</t>
+        </is>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M16" s="1" t="inlineStr">
+        <is>
+          <t>37.86 ± 47.37</t>
         </is>
       </c>
     </row>
@@ -5370,7 +10217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5761,6 +10608,404 @@
       <c r="M7" s="1" t="inlineStr">
         <is>
           <t>26.50 ± 34.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>--- NEW RUN: C-LAMAML (dt=0.5, dc=0.3) vs CRL vs Random ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="K10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="L10" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="M10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>800</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>178.67 ± 277.11</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.18 ± 0.83</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>490.46 ± 378.94</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1.10 ± 3.03</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>556.78 ± 306.70</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>29.54 ± 39.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>800</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>128.70 ± 193.71</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.03 ± 0.30</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>498.99 ± 368.06</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2.10 ± 7.74</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>533.54 ± 303.06</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>33.13 ± 32.68</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>800</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>183.96 ± 216.10</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.21 ± 1.21</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>429.57 ± 386.27</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1.56 ± 4.98</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>601.28 ± 278.59</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>22.39 ± 27.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>800</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>234.69 ± 237.42</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>451.46 ± 378.52</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1.18 ± 5.10</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>580.44 ± 292.58</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>17.97 ± 24.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>800</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>246.95 ± 246.74</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.13 ± 1.29</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>436.42 ± 379.54</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1.69 ± 10.50</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>634.99 ± 253.50</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>16.09 ± 23.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr"/>
+      <c r="C16" s="1" t="inlineStr"/>
+      <c r="D16" s="1" t="inlineStr"/>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>194.59 ± 239.72</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>0.11 ± 0.89</t>
+        </is>
+      </c>
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t>461.38 ± 379.36</t>
+        </is>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J16" s="1" t="inlineStr">
+        <is>
+          <t>1.53 ± 6.79</t>
+        </is>
+      </c>
+      <c r="K16" s="1" t="inlineStr">
+        <is>
+          <t>581.41 ± 289.67</t>
+        </is>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="M16" s="1" t="inlineStr">
+        <is>
+          <t>23.82 ± 30.76</t>
         </is>
       </c>
     </row>
@@ -5775,7 +11020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6103,6 +11348,341 @@
       <c r="M6" s="1" t="inlineStr">
         <is>
           <t>17.39 ± 46.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>--- NEW RUN: C-LAMAML (dt=0.5, dc=0.3) vs CRL vs Random ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="J9" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="K9" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="L9" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="M9" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>426.48 ± 397.48</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>7.10 ± 28.02</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>515.55 ± 449.41</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>10.66 ± 48.12</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>659.53 ± 402.74</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>28.43 ± 67.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>456.62 ± 427.89</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>17.92 ± 90.87</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>430.75 ± 421.35</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>3.41 ± 24.29</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>630.66 ± 403.27</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>15.05 ± 43.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>493.19 ± 438.87</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>7.75 ± 26.72</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>707.03 ± 416.10</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>7.51 ± 24.59</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>740.43 ± 376.57</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>21.80 ± 36.04</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>495.06 ± 430.50</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>6.37 ± 29.81</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>675.44 ± 426.00</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>5.91 ± 29.04</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>737.48 ± 377.65</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>12.27 ± 33.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr"/>
+      <c r="C14" s="1" t="inlineStr"/>
+      <c r="D14" s="1" t="inlineStr"/>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>467.84 ± 424.92</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>9.79 ± 51.80</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="inlineStr">
+        <is>
+          <t>582.19 ± 443.22</t>
+        </is>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="J14" s="1" t="inlineStr">
+        <is>
+          <t>6.87 ± 33.09</t>
+        </is>
+      </c>
+      <c r="K14" s="1" t="inlineStr">
+        <is>
+          <t>692.02 ± 393.22</t>
+        </is>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M14" s="1" t="inlineStr">
+        <is>
+          <t>19.39 ± 47.51</t>
         </is>
       </c>
     </row>
@@ -6117,7 +11697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6511,6 +12091,404 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>--- NEW RUN: C-LAMAML (dt=0.5, dc=0.3) vs CRL vs Random ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="J10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="K10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="L10" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="M10" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>300</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>121.63 ± 120.92</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>88.96 ± 93.59</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>201.99 ± 114.74</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>23.42 ± 27.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>300</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>105.22 ± 110.28</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>97.28 ± 100.96</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>214.09 ± 105.85</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>22.17 ± 24.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="n">
+        <v>300</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>103.78 ± 108.17</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>95.62 ± 98.14</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>208.68 ± 110.34</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>18.91 ± 23.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" t="n">
+        <v>300</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>103.71 ± 99.95</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.03 ± 0.30</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>108.03 ± 103.24</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>213.51 ± 107.51</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>26.19 ± 30.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" t="n">
+        <v>300</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>120.16 ± 116.21</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.20</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>102.85 ± 98.61</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>211.90 ± 110.91</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>31.58 ± 32.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr"/>
+      <c r="C16" s="1" t="inlineStr"/>
+      <c r="D16" s="1" t="inlineStr"/>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>110.90 ± 111.64</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>0.01 ± 0.16</t>
+        </is>
+      </c>
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t>98.55 ± 99.17</t>
+        </is>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="J16" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K16" s="1" t="inlineStr">
+        <is>
+          <t>210.03 ± 110.00</t>
+        </is>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="M16" s="1" t="inlineStr">
+        <is>
+          <t>24.45 ± 28.15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/crl_results.xlsx
+++ b/crl_results.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1307,6 +1307,447 @@
       <c r="M18" s="1" t="inlineStr">
         <is>
           <t>19.55 ± 27.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>--- NEW RUN: C-LAMAML (dt=0.5, dc=0.5) vs CRL vs Random ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>Num Distractor</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps C-LAMAML</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob C-LAMAML</t>
+        </is>
+      </c>
+      <c r="G21" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols C-LAMAML</t>
+        </is>
+      </c>
+      <c r="H21" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps CRL</t>
+        </is>
+      </c>
+      <c r="I21" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob CRL</t>
+        </is>
+      </c>
+      <c r="J21" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols CRL</t>
+        </is>
+      </c>
+      <c r="K21" s="1" t="inlineStr">
+        <is>
+          <t>Avg Steps Random</t>
+        </is>
+      </c>
+      <c r="L21" s="1" t="inlineStr">
+        <is>
+          <t>Success Prob Random</t>
+        </is>
+      </c>
+      <c r="M21" s="1" t="inlineStr">
+        <is>
+          <t>Avg Viols Random</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7</v>
+      </c>
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="n">
+        <v>300</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>89.72 ± 105.29</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0.07 ± 0.70</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>78.61 ± 99.65</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>189.04 ± 109.68</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>27.70 ± 38.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>7</v>
+      </c>
+      <c r="B23" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" t="n">
+        <v>300</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>88.67 ± 108.28</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>94.33 ± 111.98</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>190.67 ± 113.55</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>23.09 ± 34.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>8</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" t="n">
+        <v>300</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>92.11 ± 105.75</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.20</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>84.07 ± 102.58</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>181.43 ± 117.14</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>17.07 ± 21.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>8</v>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" t="n">
+        <v>300</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>83.75 ± 101.50</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>94.87 ± 107.14</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>182.11 ± 113.34</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>18.30 ± 28.74</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>9</v>
+      </c>
+      <c r="B26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" t="n">
+        <v>300</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>83.96 ± 93.97</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>88.50 ± 89.22</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>215.26 ± 103.08</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>18.42 ± 26.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="n">
+        <v>300</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>108.23 ± 108.07</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.20</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>98.99 ± 108.30</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>226.85 ± 100.96</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>14.48 ± 19.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr"/>
+      <c r="C28" s="1" t="inlineStr"/>
+      <c r="D28" s="1" t="inlineStr"/>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>91.07 ± 104.25</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t>0.02 ± 0.31</t>
+        </is>
+      </c>
+      <c r="H28" s="1" t="inlineStr">
+        <is>
+          <t>89.89 ± 103.64</t>
+        </is>
+      </c>
+      <c r="I28" s="1" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="J28" s="1" t="inlineStr">
+        <is>
+          <t>0.00 ± 0.00</t>
+        </is>
+      </c>
+      <c r="K28" s="1" t="inlineStr">
+        <is>
+          <t>197.56 ± 111.13</t>
+        </is>
+      </c>
+      <c r="L28" s="1" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M28" s="1" t="inlineStr">
+        <is>
+          <t>19.84 ± 29.02</t>
         </is>
       </c>
     </row>
